--- a/Output Data Tables/AFAT Outputs/Revenue Tables/2017/Revenue_by_Airline_2017.xlsx
+++ b/Output Data Tables/AFAT Outputs/Revenue Tables/2017/Revenue_by_Airline_2017.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="41" uniqueCount="41">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -169,13 +181,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
     <col min="2" max="2" width="20.7109375" customWidth="true"/>
     <col min="3" max="3" width="10.140625" customWidth="true"/>
-    <col min="4" max="4" width="10.140625" customWidth="true"/>
+    <col min="4" max="4" width="11.140625" customWidth="true"/>
     <col min="5" max="5" width="13" customWidth="true"/>
     <col min="6" max="6" width="18" customWidth="true"/>
     <col min="7" max="7" width="15.85546875" customWidth="true"/>
@@ -192,40 +204,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -1176,39 +1188,203 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>83848252170</v>
+      </c>
+      <c r="C25" s="0">
+        <v>350643870</v>
+      </c>
+      <c r="D25" s="0">
+        <v>2256095370</v>
+      </c>
+      <c r="E25" s="0">
+        <v>2874843660</v>
+      </c>
+      <c r="F25" s="0">
+        <v>386599750</v>
+      </c>
+      <c r="G25" s="0">
+        <v>0</v>
+      </c>
+      <c r="H25" s="0">
+        <v>2418258880</v>
+      </c>
+      <c r="I25" s="0">
+        <v>3075483500</v>
+      </c>
+      <c r="J25" s="0">
+        <v>0</v>
+      </c>
+      <c r="K25" s="0">
+        <v>26197309960</v>
+      </c>
+      <c r="L25" s="0">
+        <v>95210177110</v>
+      </c>
+      <c r="M25" s="0">
+        <v>121407487070</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>32155117650</v>
+      </c>
+      <c r="C26" s="0">
+        <v>34843790</v>
+      </c>
+      <c r="D26" s="0">
+        <v>336858650</v>
+      </c>
+      <c r="E26" s="0">
+        <v>564348130</v>
+      </c>
+      <c r="F26" s="0">
+        <v>58763170</v>
+      </c>
+      <c r="G26" s="0">
+        <v>683000</v>
+      </c>
+      <c r="H26" s="0">
+        <v>274639740</v>
+      </c>
+      <c r="I26" s="0">
+        <v>1891014790</v>
+      </c>
+      <c r="J26" s="0">
+        <v>10110000</v>
+      </c>
+      <c r="K26" s="0">
+        <v>1835381770</v>
+      </c>
+      <c r="L26" s="0">
+        <v>35326374920</v>
+      </c>
+      <c r="M26" s="0">
+        <v>37161756690</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>3979074580</v>
+      </c>
+      <c r="C27" s="0">
+        <v>3953150</v>
+      </c>
+      <c r="D27" s="0">
+        <v>1527080</v>
+      </c>
+      <c r="E27" s="0">
+        <v>1069460050</v>
+      </c>
+      <c r="F27" s="0">
+        <v>229275160</v>
+      </c>
+      <c r="G27" s="0">
+        <v>0</v>
+      </c>
+      <c r="H27" s="0">
+        <v>118583360</v>
+      </c>
+      <c r="I27" s="0">
+        <v>648777720</v>
+      </c>
+      <c r="J27" s="0">
+        <v>0</v>
+      </c>
+      <c r="K27" s="0">
+        <v>623275580</v>
+      </c>
+      <c r="L27" s="0">
+        <v>6050651040</v>
+      </c>
+      <c r="M27" s="0">
+        <v>6673926620</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>7126522420</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0</v>
+      </c>
+      <c r="D28" s="0">
+        <v>13000</v>
+      </c>
+      <c r="E28" s="0">
+        <v>270</v>
+      </c>
+      <c r="F28" s="0">
+        <v>91130</v>
+      </c>
+      <c r="G28" s="0">
+        <v>0</v>
+      </c>
+      <c r="H28" s="0">
+        <v>0</v>
+      </c>
+      <c r="I28" s="0">
+        <v>23447890</v>
+      </c>
+      <c r="J28" s="0">
+        <v>55458000</v>
+      </c>
+      <c r="K28" s="0">
+        <v>18171970</v>
+      </c>
+      <c r="L28" s="0">
+        <v>7205531700</v>
+      </c>
+      <c r="M28" s="0">
+        <v>7223703670</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>127108966820</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>389440810</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>2594494100</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>4508652110</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>674729210</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>683000</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>2811481980</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>5638723900</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>65568000</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>28674139280</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>143792734770</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>172466874050</v>
       </c>
     </row>
